--- a/ConvertData/EXCEL_BoltsSP16/TableBoltsSP16.xlsx
+++ b/ConvertData/EXCEL_BoltsSP16/TableBoltsSP16.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\length\source\repos\ConvertData\ConvertData\EXCEL_BoltsSP16\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\Programmings\ForWorking\ConvertData\ConvertData\EXCEL_BoltsSP16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD5E8FD-CC55-4685-B631-B21981A42044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32619C8-986F-4467-AA93-F47102F85BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bolts" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
   <si>
-    <t>Ab</t>
+    <t>GOST_bolts</t>
   </si>
   <si>
-    <t>Abn</t>
+    <t>СП 16.13330</t>
   </si>
   <si>
-    <t>d</t>
+    <t>d_SP16</t>
+  </si>
+  <si>
+    <t>Ab_SP16</t>
+  </si>
+  <si>
+    <t>Abn_SP16</t>
   </si>
 </sst>
 </file>
@@ -408,127 +414,163 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>16</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>2.0099999999999998</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1.57</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>18</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>2.54</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1.92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
         <v>20</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>3.14</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
         <v>22</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>3.8</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>3.03</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>24</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>4.5199999999999996</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>3.53</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>27</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>5.72</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>4.59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>30</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>7.06</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>5.61</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>36</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>10.17</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>8.16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
         <v>42</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>13.85</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>11.2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>48</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>18.09</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>14.72</v>
       </c>
     </row>

--- a/ConvertData/EXCEL_BoltsSP16/TableBoltsSP16.xlsx
+++ b/ConvertData/EXCEL_BoltsSP16/TableBoltsSP16.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\Programmings\ForWorking\ConvertData\ConvertData\EXCEL_BoltsSP16\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\length\source\repos\ConvertData\ConvertData\EXCEL_BoltsSP16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32619C8-986F-4467-AA93-F47102F85BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD5E8FD-CC55-4685-B631-B21981A42044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bolts" sheetId="1" r:id="rId1"/>
@@ -25,21 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>GOST_bolts</t>
+    <t>Ab</t>
   </si>
   <si>
-    <t>СП 16.13330</t>
+    <t>Abn</t>
   </si>
   <si>
-    <t>d_SP16</t>
-  </si>
-  <si>
-    <t>Ab_SP16</t>
-  </si>
-  <si>
-    <t>Abn_SP16</t>
+    <t>d</t>
   </si>
 </sst>
 </file>
@@ -414,163 +408,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
       <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
         <v>1</v>
       </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>16</v>
+      </c>
       <c r="B2">
-        <v>16</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="C2">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="D2">
         <v>1.57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>2.54</v>
       </c>
       <c r="C3">
-        <v>2.54</v>
-      </c>
-      <c r="D3">
         <v>1.92</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>3.14</v>
       </c>
       <c r="C4">
-        <v>3.14</v>
-      </c>
-      <c r="D4">
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>1</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>22</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>3.8</v>
       </c>
       <c r="C5">
-        <v>3.8</v>
-      </c>
-      <c r="D5">
         <v>3.03</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>1</v>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>24</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="C6">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="D6">
         <v>3.53</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>1</v>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>5.72</v>
       </c>
       <c r="C7">
-        <v>5.72</v>
-      </c>
-      <c r="D7">
         <v>4.59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>1</v>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>30</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>7.06</v>
       </c>
       <c r="C8">
-        <v>7.06</v>
-      </c>
-      <c r="D8">
         <v>5.61</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>1</v>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>36</v>
       </c>
       <c r="B9">
-        <v>36</v>
+        <v>10.17</v>
       </c>
       <c r="C9">
-        <v>10.17</v>
-      </c>
-      <c r="D9">
         <v>8.16</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>1</v>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>42</v>
       </c>
       <c r="B10">
-        <v>42</v>
+        <v>13.85</v>
       </c>
       <c r="C10">
-        <v>13.85</v>
-      </c>
-      <c r="D10">
         <v>11.2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>1</v>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>48</v>
       </c>
       <c r="B11">
-        <v>48</v>
+        <v>18.09</v>
       </c>
       <c r="C11">
-        <v>18.09</v>
-      </c>
-      <c r="D11">
         <v>14.72</v>
       </c>
     </row>
